--- a/artfynd/A 54208-2021 artfynd.xlsx
+++ b/artfynd/A 54208-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54208-2021 artfynd.xlsx
+++ b/artfynd/A 54208-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4747,6 +4747,336 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114899841</v>
+      </c>
+      <c r="B35" t="n">
+        <v>82999</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Femstaven, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>592350</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6573952</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Dan Åman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Dan Åman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114899663</v>
+      </c>
+      <c r="B36" t="n">
+        <v>82999</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Femstaven, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>592297</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6573897</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Dan Åman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Dan Åman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114899749</v>
+      </c>
+      <c r="B37" t="n">
+        <v>82999</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Femstaven, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>592345</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6573935</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Dan Åman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Dan Åman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54208-2021 artfynd.xlsx
+++ b/artfynd/A 54208-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75862887</v>
+        <v>99590791</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogen, Srm</t>
+          <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592112.8384556185</v>
+        <v>592339</v>
       </c>
       <c r="R2" t="n">
-        <v>6573920.055725398</v>
+        <v>6573753</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-01-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-01-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +762,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson, Markus Forsberg</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99586879</v>
+        <v>96982662</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,35 +785,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kälbro, Srm</t>
+          <t>Ärla NV, Femstaven, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592024.6902909365</v>
+        <v>592185</v>
       </c>
       <c r="R3" t="n">
-        <v>6573966.46169783</v>
+        <v>6574110</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -858,22 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på algbevuxen humus, invid granstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,77 +874,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99587622</v>
+        <v>75862887</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kälbro, Srm</t>
+          <t>Skogen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592132.5574300073</v>
+        <v>592113</v>
       </c>
       <c r="R4" t="n">
-        <v>6573782.56172271</v>
+        <v>6573920</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-01-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-01-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,73 +983,58 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Fredrik Enoksson, Markus Forsberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99590759</v>
+        <v>99587192</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592305.1187007042</v>
+        <v>592158</v>
       </c>
       <c r="R5" t="n">
-        <v>6573759.671069324</v>
+        <v>6573875</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1102,19 +1064,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,55 +1093,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99590791</v>
+        <v>100781607</v>
       </c>
       <c r="B6" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592339.0595442618</v>
+        <v>592339</v>
       </c>
       <c r="R6" t="n">
-        <v>6573753.34245983</v>
+        <v>6573930</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,22 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,80 +1183,76 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99590608</v>
+        <v>114899663</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kälbro, Srm</t>
+          <t>Femstaven, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592218.091023531</v>
+        <v>592297</v>
       </c>
       <c r="R7" t="n">
-        <v>6573738.647288655</v>
+        <v>6573898</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,22 +1276,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,73 +1290,74 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99587480</v>
+        <v>114899749</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kälbro, Srm</t>
+          <t>Femstaven, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592155.3754945004</v>
+        <v>592345</v>
       </c>
       <c r="R8" t="n">
-        <v>6573833.70637676</v>
+        <v>6573935</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,22 +1381,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,82 +1395,74 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99591237</v>
+        <v>114899841</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kälbro, Srm</t>
+          <t>Femstaven, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592157.2979000411</v>
+        <v>592350</v>
       </c>
       <c r="R9" t="n">
-        <v>6573838.863186746</v>
+        <v>6573952</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,22 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,72 +1500,74 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99587192</v>
+        <v>114899861</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kälbro, Srm</t>
+          <t>Femstaven, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592157.4528975509</v>
+        <v>592361</v>
       </c>
       <c r="R10" t="n">
-        <v>6573874.637622888</v>
+        <v>6573966</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,22 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,74 +1605,65 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99587535</v>
+        <v>102822015</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592155.7320768421</v>
+        <v>591944</v>
       </c>
       <c r="R11" t="n">
-        <v>6573797.943981688</v>
+        <v>6573988</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1804,22 +1690,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,61 +1732,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99591277</v>
+        <v>99586879</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592226.9262657581</v>
+        <v>592024</v>
       </c>
       <c r="R12" t="n">
-        <v>6573838.510758052</v>
+        <v>6573966</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1930,19 +1801,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,12 +1833,7 @@
         <v>99587954</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592121.8630898207</v>
+        <v>592121</v>
       </c>
       <c r="R13" t="n">
-        <v>6573780.258014164</v>
+        <v>6573781</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2043,19 +1899,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,61 +1928,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99590749</v>
+        <v>96982674</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kälbro, Srm</t>
+          <t>Ärla NV, Femstaven, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592305.1187007042</v>
+        <v>592170</v>
       </c>
       <c r="R14" t="n">
-        <v>6573759.671069324</v>
+        <v>6574005</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2163,22 +2004,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,33 +2018,54 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies # låga</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99590657</v>
+        <v>99586582</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2092,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2252,14 +2104,14 @@
       <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kälbro, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592205.8893881848</v>
+        <v>591988</v>
       </c>
       <c r="R15" t="n">
-        <v>6573756.23665901</v>
+        <v>6573861</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2291,7 +2143,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2301,7 +2153,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2328,15 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99587894</v>
+        <v>99587424</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2210,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2379,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592128.9513207781</v>
+        <v>592170</v>
       </c>
       <c r="R16" t="n">
-        <v>6573783.496210905</v>
+        <v>6573852</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2412,19 +2259,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,15 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99590679</v>
+        <v>99587480</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,16 +2316,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2502,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592231.9323281839</v>
+        <v>592155</v>
       </c>
       <c r="R17" t="n">
-        <v>6573758.913630998</v>
+        <v>6573834</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2535,19 +2358,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,15 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99587597</v>
+        <v>99587535</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,12 +2417,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2625,10 +2428,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592152.4887611484</v>
+        <v>592156</v>
       </c>
       <c r="R18" t="n">
-        <v>6573805.019456581</v>
+        <v>6573798</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2658,19 +2461,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2697,15 +2490,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99590938</v>
+        <v>99587597</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2520,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2748,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592328.4440883412</v>
+        <v>592153</v>
       </c>
       <c r="R19" t="n">
-        <v>6573789.877777471</v>
+        <v>6573805</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2781,19 +2569,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,15 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99587424</v>
+        <v>99587622</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,12 +2628,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2871,10 +2639,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592169.7779882768</v>
+        <v>592133</v>
       </c>
       <c r="R20" t="n">
-        <v>6573851.94157628</v>
+        <v>6573783</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2904,19 +2672,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2943,15 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>100781792</v>
+        <v>99587894</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2978,27 +2731,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592171.037237288</v>
+        <v>592128</v>
       </c>
       <c r="R21" t="n">
-        <v>6573757.945100446</v>
+        <v>6573784</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3022,27 +2777,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>35 bladrosetter</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3053,36 +2793,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>100781777</v>
+        <v>99590471</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3109,27 +2839,29 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592150.395827607</v>
+        <v>592192</v>
       </c>
       <c r="R22" t="n">
-        <v>6573827.964304216</v>
+        <v>6573677</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3153,27 +2885,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>4 bladrosetter</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3184,36 +2901,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>100781796</v>
+        <v>99590491</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,27 +2947,29 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592310.9949830773</v>
+        <v>592173</v>
       </c>
       <c r="R23" t="n">
-        <v>6573749.593520008</v>
+        <v>6573668</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3284,27 +2993,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>6 bladrosetter</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3315,36 +3009,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>100781799</v>
+        <v>99590608</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,27 +3055,29 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592310.7736082906</v>
+        <v>592219</v>
       </c>
       <c r="R24" t="n">
-        <v>6573779.738498771</v>
+        <v>6573738</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3415,27 +3101,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 bladrosetter</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3446,36 +3117,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrskog, sank</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>100781607</v>
+        <v>99590657</v>
       </c>
       <c r="B25" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,46 +3144,48 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592338.8525000685</v>
+        <v>592206</v>
       </c>
       <c r="R25" t="n">
-        <v>6573930.147921201</v>
+        <v>6573757</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3546,22 +3209,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3572,36 +3225,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>100781803</v>
+        <v>99590679</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,27 +3271,29 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592350.2611477112</v>
+        <v>592232</v>
       </c>
       <c r="R26" t="n">
-        <v>6573839.977274905</v>
+        <v>6573758</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3672,27 +3317,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>80 bladrosetter</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3703,36 +3333,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>100781795</v>
+        <v>99590749</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3759,27 +3379,29 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592251.3588579072</v>
+        <v>592305</v>
       </c>
       <c r="R27" t="n">
-        <v>6573738.944849088</v>
+        <v>6573760</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3803,27 +3425,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>47 bladrosetter</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,36 +3441,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>100781772</v>
+        <v>99590938</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3890,27 +3487,29 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592160.3644806459</v>
+        <v>592329</v>
       </c>
       <c r="R28" t="n">
-        <v>6573817.986112537</v>
+        <v>6573790</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3934,27 +3533,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3965,36 +3549,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>100781794</v>
+        <v>99591237</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4021,27 +3595,29 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592211.4399392203</v>
+        <v>592157</v>
       </c>
       <c r="R29" t="n">
-        <v>6573738.485666699</v>
+        <v>6573839</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4065,27 +3641,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>35 bladrosetter</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4096,63 +3657,53 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>100781798</v>
+        <v>99591277</v>
       </c>
       <c r="B30" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4160,19 +3711,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592310.9949830773</v>
+        <v>592227</v>
       </c>
       <c r="R30" t="n">
-        <v>6573749.593520008</v>
+        <v>6573839</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4196,22 +3749,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4222,36 +3765,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Ylva Linnman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>100781793</v>
+        <v>100781772</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4278,7 +3811,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4292,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592200.9593252409</v>
+        <v>592160</v>
       </c>
       <c r="R31" t="n">
-        <v>6573748.451513059</v>
+        <v>6573818</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4325,24 +3858,14 @@
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>36 bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4356,7 +3879,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4374,15 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>100781800</v>
+        <v>100781774</v>
       </c>
       <c r="B32" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4409,7 +3927,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4423,10 +3941,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592311.4795047514</v>
+        <v>592140</v>
       </c>
       <c r="R32" t="n">
-        <v>6573729.675273817</v>
+        <v>6573818</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4456,24 +3974,14 @@
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>7 bladrosetter</t>
+          <t>19 bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4505,15 +4013,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>100781774</v>
+        <v>100781777</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4043,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4554,10 +4057,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592140.4116469632</v>
+        <v>592150</v>
       </c>
       <c r="R33" t="n">
-        <v>6573817.50158162</v>
+        <v>6573828</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4587,24 +4090,14 @@
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>19 bladrosetter</t>
+          <t>4 bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4636,54 +4129,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>102822015</v>
+        <v>100781792</v>
       </c>
       <c r="B34" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591944.312864006</v>
+        <v>592171</v>
       </c>
       <c r="R34" t="n">
-        <v>6573988.01886756</v>
+        <v>6573758</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4707,22 +4203,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>35 bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4733,31 +4224,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ylva Linnman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>114899663</v>
+        <v>100781793</v>
       </c>
       <c r="B35" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4765,41 +4256,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Femstaven, Srm</t>
+          <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592297</v>
+        <v>592201</v>
       </c>
       <c r="R35" t="n">
-        <v>6573898</v>
+        <v>6573748</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4826,12 +4319,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-04-21</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-04-21</t>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>36 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4840,34 +4338,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>114899841</v>
+        <v>100781794</v>
       </c>
       <c r="B36" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4875,41 +4372,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Femstaven, Srm</t>
+          <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592350</v>
+        <v>592211</v>
       </c>
       <c r="R36" t="n">
-        <v>6573952</v>
+        <v>6573738</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4936,12 +4435,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-04-21</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-04-21</t>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>35 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4950,34 +4454,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>114899749</v>
+        <v>100781795</v>
       </c>
       <c r="B37" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4985,41 +4488,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1445</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Femstaven, Srm</t>
+          <t>Kälbro, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592345</v>
+        <v>592251</v>
       </c>
       <c r="R37" t="n">
-        <v>6573935</v>
+        <v>6573739</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5046,12 +4551,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-04-21</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-04-21</t>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>47 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5060,22 +4570,811 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>100781796</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kälbro, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>592311</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6573750</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>6 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>100781799</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kälbro, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>592311</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6573780</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Barrskog, sank</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>100781800</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kälbro, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>592311</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6573730</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>100781803</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kälbro, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>592350</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6573840</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>80 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>99590759</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kälbro, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>592305</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6573760</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>100781798</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kälbro, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>592311</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6573750</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>100781771</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kälbro, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>592269</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6573899</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Glänta i barrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54208-2021 artfynd.xlsx
+++ b/artfynd/A 54208-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590791</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96982662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75862887</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99587192</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781607</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114899663</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114899749</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114899841</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114899861</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,6 +1779,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102822015</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99586879</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99587954</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2059,6 +2124,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96982674</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2177,6 +2247,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99586582</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2285,6 +2360,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99587424</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99587480</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2487,6 +2572,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99587535</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2595,6 +2685,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99587597</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2698,6 +2793,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99587622</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2806,6 +2906,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99587894</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2914,6 +3019,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590471</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3022,6 +3132,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590491</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3130,6 +3245,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590608</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3238,6 +3358,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590657</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3346,6 +3471,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590679</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590749</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3562,6 +3697,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590938</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3670,6 +3810,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99591237</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3778,6 +3923,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99591277</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3894,6 +4044,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781772</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4010,6 +4165,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781774</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4126,6 +4286,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781777</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4242,6 +4407,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781792</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4358,6 +4528,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781793</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4474,6 +4649,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781794</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4590,6 +4770,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781795</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4706,6 +4891,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781796</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4822,6 +5012,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781799</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4938,6 +5133,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781800</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5054,6 +5254,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781803</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5162,6 +5367,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590759</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5273,6 +5483,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781798</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5375,8 +5590,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100781771</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>